--- a/細川/GoogleAIStudio/テストコード/output/plan_input_tasks.xlsx
+++ b/細川/GoogleAIStudio/テストコード/output/plan_input_tasks.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="タスク一覧" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH44"/>
+  <dimension ref="A1:AI44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,115 +486,120 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>加工内容</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>加工完了区分</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>実加工数</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>実出来高</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>加工工程の決定プロセスの因子</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>（元）必要人数</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>必要人数</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>（元）加工速度_上書き</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>加工速度_上書き</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>（元）タスク加工効率</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>タスク加工効率</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>（元）優先度</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>優先度</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>（元）指定納期_上書き</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>指定納期_上書き</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>（元）加工開始日_指定</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>加工開始日_指定</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>（元）加工開始時刻_指定</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>加工開始時刻_指定</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>（元）担当OP_指定</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>担当OP_指定</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>（元）特別指定_備考</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>特別指定_備考</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>AI特別指定_解析</t>
         </is>
@@ -642,74 +647,79 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>5700</v>
-      </c>
       <c r="N2" t="n">
-        <v>5700</v>
-      </c>
-      <c r="O2" t="inlineStr">
+        <v>9000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6600</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>検査+熱融着機　湖南</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>（1）</t>
         </is>
       </c>
-      <c r="Q2" s="3" t="n"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>（8）</t>
         </is>
       </c>
-      <c r="S2" s="3" t="n"/>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U2" s="3" t="n"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W2" s="3" t="n"/>
-      <c r="X2" t="inlineStr">
+      <c r="T2" s="3" t="n"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="n"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X2" s="3" t="n"/>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="n"/>
-      <c r="Z2" t="inlineStr">
+      <c r="Z2" s="3" t="n"/>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>（2026/3/18）</t>
         </is>
       </c>
-      <c r="AA2" s="3" t="n"/>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC2" s="3" t="n"/>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE2" s="3" t="n"/>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG2" s="3" t="inlineStr">
+      <c r="AB2" s="3" t="n"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD2" s="3" t="n"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF2" s="3" t="n"/>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH2" s="3" t="inlineStr">
         <is>
           <t>担当者を富田さんへ固定</t>
         </is>
@@ -719,31 +729,31 @@
       <c r="A3" s="3" t="n"/>
       <c r="B3" t="inlineStr">
         <is>
-          <t>W3-13</t>
+          <t>V4-1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>スライス</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>スライス機1　湖南</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="F3" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>16.12</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>15020-JX5R-1300X300F-A   R</t>
+          <t>30020-BG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
@@ -753,84 +763,89 @@
         <v>46115</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>46104</v>
+        <v>46113</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>検査+熱融着機　湖南</t>
-        </is>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="n"/>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>（8）</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="n"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" t="inlineStr">
+          <t>スライス+スライス機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>（2）</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>（16.12）</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="n"/>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="n"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="n"/>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>（2026/3/23）</t>
-        </is>
-      </c>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC3" s="3" t="n"/>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE3" s="3" t="n"/>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG3" s="3" t="n"/>
+      <c r="Z3" s="3" t="n"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>（2026/4/1）</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="n"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="n"/>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="n"/>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>V4-1</t>
+          <t>Y4-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,10 +859,10 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F4" t="n">
         <v>2000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4000</v>
       </c>
       <c r="G4" t="n">
         <v>16.12</v>
@@ -868,80 +883,85 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" t="inlineStr">
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S4" s="3" t="n"/>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" t="inlineStr">
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" t="inlineStr">
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA4" s="3" t="n"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC4" s="3" t="n"/>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE4" s="3" t="n"/>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG4" s="3" t="n"/>
+      <c r="AB4" s="3" t="n"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="n"/>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="n"/>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>V4-2</t>
+          <t>Y4-11</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -965,7 +985,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>30020-BG00-1000X200F-A   C</t>
+          <t>30020-BG00-1030X200F-ABK0C</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -979,80 +999,85 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" t="inlineStr">
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S5" s="3" t="n"/>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" t="inlineStr">
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" t="inlineStr">
+      <c r="Z5" s="3" t="n"/>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC5" s="3" t="n"/>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE5" s="3" t="n"/>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG5" s="3" t="n"/>
+      <c r="AB5" s="3" t="n"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD5" s="3" t="n"/>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF5" s="3" t="n"/>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>V4-3</t>
+          <t>V4-2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1066,17 +1091,17 @@
         </is>
       </c>
       <c r="E6" t="n">
+        <v>200</v>
+      </c>
+      <c r="F6" t="n">
         <v>400</v>
-      </c>
-      <c r="F6" t="n">
-        <v>800</v>
       </c>
       <c r="G6" t="n">
         <v>16.12</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>30030-BG00-1000X100F-ABK0C</t>
+          <t>30020-BG00-1000X200F-A   C</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
@@ -1090,80 +1115,85 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q6" s="3" t="n"/>
-      <c r="R6" t="inlineStr">
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S6" s="3" t="n"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" t="inlineStr">
+      <c r="T6" s="3" t="n"/>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="n"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="n"/>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" s="3" t="n"/>
+      <c r="AA6" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC6" s="3" t="n"/>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE6" s="3" t="n"/>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG6" s="3" t="n"/>
+      <c r="AB6" s="3" t="n"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="n"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="n"/>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Y4-1</t>
+          <t>V4-3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1177,17 +1207,17 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>2000</v>
+        <v>800</v>
       </c>
       <c r="G7" t="n">
         <v>16.12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>30020-BG00-1030X200F-ABK0C</t>
+          <t>30030-BG00-1000X100F-ABK0C</t>
         </is>
       </c>
       <c r="I7" s="2" t="n">
@@ -1201,74 +1231,79 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q7" s="3" t="n"/>
-      <c r="R7" t="inlineStr">
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S7" s="3" t="n"/>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" t="inlineStr">
+      <c r="T7" s="3" t="n"/>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="n"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="n"/>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" t="inlineStr">
+      <c r="Z7" s="3" t="n"/>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="n"/>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE7" s="3" t="n"/>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG7" s="3" t="n"/>
+      <c r="AB7" s="3" t="n"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="n"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="n"/>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
@@ -1312,74 +1347,79 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
       <c r="N8" t="n">
         <v>0</v>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>EC+SEC機　湖南</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q8" s="3" t="n"/>
-      <c r="R8" t="inlineStr">
+      <c r="R8" s="3" t="n"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>（18.06）</t>
         </is>
       </c>
-      <c r="S8" s="3" t="n"/>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" t="inlineStr">
+      <c r="T8" s="3" t="n"/>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="n"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="n"/>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" t="inlineStr">
+      <c r="Z8" s="3" t="n"/>
+      <c r="AA8" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA8" s="3" t="n"/>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC8" s="3" t="n"/>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE8" s="3" t="n"/>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG8" s="3" t="n"/>
+      <c r="AB8" s="3" t="n"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="n"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="n"/>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1427,104 +1467,109 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>梱包,EC</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="inlineStr">
         <is>
           <t>梱包+SEC機　湖南</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q9" s="3" t="n"/>
-      <c r="R9" t="inlineStr">
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>（0）</t>
         </is>
       </c>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" t="inlineStr">
+      <c r="T9" s="3" t="n"/>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="n"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="n"/>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="n"/>
-      <c r="Z9" t="inlineStr">
+      <c r="Z9" s="3" t="n"/>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC9" s="3" t="n"/>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE9" s="3" t="n"/>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG9" s="3" t="n"/>
+      <c r="AB9" s="3" t="n"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="n"/>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="n"/>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Y4-11</t>
+          <t>W3-13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>スライス</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>スライス機1　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>200</v>
+        <v>6000</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>6000</v>
       </c>
       <c r="G10" t="n">
-        <v>16.12</v>
+        <v>8</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>30020-BG00-1030X200F-ABK0C</t>
+          <t>15020-JX5R-1300X300F-A   R</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
@@ -1534,108 +1579,113 @@
         <v>46115</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>46113</v>
+        <v>46104</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="n">
         <v>0</v>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>スライス+スライス機1　湖南</t>
-        </is>
+      <c r="O10" t="n">
+        <v>0</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>（2）</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="n"/>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>（16.12）</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" t="inlineStr">
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>（8）</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="n"/>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="n"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="n"/>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>（2026/4/1）</t>
-        </is>
-      </c>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC10" s="3" t="n"/>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE10" s="3" t="n"/>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG10" s="3" t="n"/>
+      <c r="Z10" s="3" t="n"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>（2026/3/23）</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="n"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="n"/>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="n"/>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Y3-30</t>
+          <t>W4-1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>5700</v>
       </c>
       <c r="F11" t="n">
-        <v>800</v>
+        <v>5700</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>18.06</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10010-FY00- 740X200F-AGR0C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="I11" s="2" t="n">
@@ -1649,104 +1699,113 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>エンボス+エンボス　湖南</t>
-        </is>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>（2）</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="n"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>（10）</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="n"/>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" t="inlineStr">
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>（3）</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>（18.06）</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="n"/>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="n"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="n"/>
+      <c r="Y11" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" t="inlineStr">
+      <c r="Z11" s="3" t="n"/>
+      <c r="AA11" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA11" s="3" t="n"/>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="n"/>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE11" s="3" t="n"/>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG11" s="3" t="n"/>
+      <c r="AB11" s="3" t="n"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="n"/>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="n"/>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n"/>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>V4-4</t>
+          <t>Y4-2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="F12" t="n">
-        <v>1600</v>
+        <v>1200</v>
       </c>
       <c r="G12" t="n">
         <v>15</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>30030-AT60-1000X200F-A   C</t>
+          <t>25020-FG00- 740X200F-AGR0M</t>
         </is>
       </c>
       <c r="I12" s="2" t="n">
@@ -1756,108 +1815,113 @@
         <v>46118</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
       <c r="N12" t="n">
         <v>0</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>接続+熱融着機　湖南</t>
-        </is>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>分割+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>（1）</t>
         </is>
       </c>
-      <c r="Q12" s="3" t="n"/>
-      <c r="R12" t="inlineStr">
+      <c r="R12" s="3" t="n"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>（15）</t>
         </is>
       </c>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" t="inlineStr">
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="n"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="n"/>
+      <c r="Y12" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>（2026/4/1）</t>
-        </is>
-      </c>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC12" s="3" t="n"/>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE12" s="3" t="n"/>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG12" s="3" t="n"/>
+      <c r="Z12" s="3" t="n"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>（2026/4/2）</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="n"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="n"/>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="n"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>V4-5</t>
+          <t>Y3-30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="G13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>30040-AS60-1000X200F-A   C</t>
+          <t>10010-FY00- 740X200F-AGR0C</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1871,81 +1935,82 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
+          <t>エンボス</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>接続+熱融着機　湖南</t>
-        </is>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>（15）</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" t="inlineStr">
+          <t>エンボス+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>（2）</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="n"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="n"/>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="n"/>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="n"/>
+      <c r="Y13" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" t="inlineStr">
+      <c r="Z13" s="3" t="n"/>
+      <c r="AA13" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC13" s="3" t="n"/>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE13" s="3" t="n"/>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG13" s="3" t="n"/>
+      <c r="AB13" s="3" t="n"/>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="n"/>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="n"/>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A14" s="3" t="n"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>Y4-2</t>
@@ -1953,7 +2018,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1968,7 +2033,7 @@
         <v>1200</v>
       </c>
       <c r="G14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1986,104 +2051,109 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>分割+エンボス　湖南</t>
-        </is>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="n"/>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>（15）</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" t="inlineStr">
+          <t>エンボス+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>（2）</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n"/>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="n"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="n"/>
+      <c r="Y14" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" s="3" t="n"/>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC14" s="3" t="n"/>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE14" s="3" t="n"/>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG14" s="3" t="n"/>
+      <c r="AB14" s="3" t="n"/>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="n"/>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="n"/>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Y4-2</t>
+          <t>V4-4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="F15" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>25020-FG00- 740X200F-AGR0M</t>
+          <t>30030-AT60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -2093,108 +2163,113 @@
         <v>46118</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>エンボス+エンボス　湖南</t>
-        </is>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>（2）</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="n"/>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>（10）</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" t="inlineStr">
+          <t>接続+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>（15）</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="n"/>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="n"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="n"/>
+      <c r="Y15" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>（2026/4/2）</t>
-        </is>
-      </c>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="n"/>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE15" s="3" t="n"/>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG15" s="3" t="n"/>
+      <c r="Z15" s="3" t="n"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>（2026/4/1）</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="n"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="n"/>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="n"/>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>W4-1</t>
+          <t>V4-5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="F16" t="n">
-        <v>5700</v>
+        <v>1200</v>
       </c>
       <c r="G16" t="n">
-        <v>18.06</v>
+        <v>15</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>30040-AS60-1000X200F-A   C</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -2208,74 +2283,79 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>接続</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>EC+EC機　湖南</t>
-        </is>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>（3）</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="n"/>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>（18.06）</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" t="inlineStr">
+          <t>接続+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>（15）</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="n"/>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="n"/>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="n"/>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" s="3" t="n"/>
+      <c r="AA16" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC16" s="3" t="n"/>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE16" s="3" t="n"/>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG16" s="3" t="n"/>
+      <c r="AB16" s="3" t="n"/>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="n"/>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="n"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
@@ -2319,104 +2399,109 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>検査+熱融着機　湖南</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>（1）</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="n"/>
-      <c r="R17" t="inlineStr">
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>（9.04）</t>
         </is>
       </c>
-      <c r="S17" s="3" t="n"/>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" t="inlineStr">
+      <c r="T17" s="3" t="n"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="n"/>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="n"/>
+      <c r="Y17" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" s="3" t="n"/>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>（2026/4/1）</t>
         </is>
       </c>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC17" s="3" t="n"/>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE17" s="3" t="n"/>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG17" s="3" t="n"/>
+      <c r="AB17" s="3" t="n"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="n"/>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="n"/>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Y3-26</t>
+          <t>W4-4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6400</v>
+        <v>500</v>
       </c>
       <c r="F18" t="n">
-        <v>12800</v>
+        <v>500</v>
       </c>
       <c r="G18" t="n">
-        <v>25</v>
+        <v>18.06</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>25025-JP66-1160X250F-A   Q</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -2430,78 +2515,79 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>スリット,EC</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>SEC+SEC機　湖南</t>
-        </is>
+      <c r="O18" t="n">
+        <v>0</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="n"/>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>（25）</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="n"/>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" t="inlineStr">
+      <c r="R18" s="3" t="n"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>（18.06）</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="n"/>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="n"/>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="n"/>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>（2026/4/7）</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" s="3" t="n"/>
+      <c r="AA18" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA18" s="3" t="n"/>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC18" s="3" t="n"/>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE18" s="3" t="n"/>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG18" s="3" t="inlineStr">
-        <is>
-          <t>4/5に少なくとも2000m出荷したいので間に合うように計画を変更する</t>
-        </is>
-      </c>
+      <c r="AB18" s="3" t="n"/>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="n"/>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="n"/>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n"/>
@@ -2512,12 +2598,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2527,7 +2613,7 @@
         <v>500</v>
       </c>
       <c r="G19" t="n">
-        <v>18.06</v>
+        <v>10.12</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2545,104 +2631,109 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
+          <t>スリット,EC</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>EC+EC機　湖南</t>
-        </is>
+      <c r="O19" t="n">
+        <v>0</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>（3）</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="n"/>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>（18.06）</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="n"/>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" t="inlineStr">
+          <t>スリット+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>（2）</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>（10.12）</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="n"/>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="n"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="n"/>
+      <c r="Y19" t="inlineStr">
         <is>
           <t>（2026/4/7）</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="n"/>
-      <c r="Z19" t="inlineStr">
+      <c r="Z19" s="3" t="n"/>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA19" s="3" t="n"/>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC19" s="3" t="n"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE19" s="3" t="n"/>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG19" s="3" t="n"/>
+      <c r="AB19" s="3" t="n"/>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="n"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="n"/>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>W4-4</t>
+          <t>Y3-26</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>500</v>
+        <v>6400</v>
       </c>
       <c r="F20" t="n">
-        <v>500</v>
+        <v>12800</v>
       </c>
       <c r="G20" t="n">
-        <v>10.12</v>
+        <v>25</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>25025-JP66-1160X250F-A   Q</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -2656,108 +2747,113 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>0</v>
-      </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>スリット+スリット機1　湖南</t>
-        </is>
+      <c r="O20" t="n">
+        <v>0</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>（2）</t>
-        </is>
-      </c>
-      <c r="Q20" s="3" t="n"/>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>（10.12）</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="n"/>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" t="inlineStr">
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>（3）</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>（25）</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="n"/>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="n"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="n"/>
+      <c r="Y20" t="inlineStr">
         <is>
           <t>（2026/4/7）</t>
         </is>
       </c>
-      <c r="Y20" s="3" t="n"/>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" s="3" t="n"/>
+      <c r="AA20" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA20" s="3" t="n"/>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC20" s="3" t="n"/>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE20" s="3" t="n"/>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG20" s="3" t="n"/>
+      <c r="AB20" s="3" t="n"/>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="n"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="n"/>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>4/5に少なくとも2000m出荷したいので間に合うように計画を変更する</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A21" s="3" t="n"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Y4-3</t>
+          <t>T4-1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>分割</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>EC機　湖南</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="F21" t="n">
-        <v>2800</v>
+        <v>1000</v>
       </c>
       <c r="G21" t="n">
-        <v>15</v>
+        <v>18.06</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>19022-FG00- 940X200F-AGR2M</t>
+          <t>30040-JG00-1030X200F-ABK0Q</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
@@ -2767,108 +2863,113 @@
         <v>46120</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>46113</v>
+        <v>46115</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
+          <t>EC</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>分割+スリット機1　湖南</t>
-        </is>
+      <c r="O21" t="n">
+        <v>0</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q21" s="3" t="n"/>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>（15）</t>
-        </is>
-      </c>
-      <c r="S21" s="3" t="n"/>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" t="inlineStr">
+          <t>EC+EC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>（3）</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="n"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>（18.06）</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="n"/>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="n"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="n"/>
+      <c r="Y21" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>（2026/4/1）</t>
-        </is>
-      </c>
-      <c r="AA21" s="3" t="n"/>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC21" s="3" t="n"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE21" s="3" t="n"/>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG21" s="3" t="n"/>
+      <c r="Z21" s="3" t="n"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>（2026/4/3）</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="n"/>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="n"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="n"/>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Y4-3</t>
+          <t>JR260401</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>エンボス</t>
+          <t>スリット</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>エンボス　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2800</v>
+        <v>950</v>
       </c>
       <c r="F22" t="n">
-        <v>2800</v>
+        <v>950</v>
       </c>
       <c r="G22" t="n">
-        <v>10</v>
+        <v>10.12</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>19022-FG00- 940X200F-AGR2M</t>
+          <t>40040-R10W- 870X 95  LG</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
@@ -2878,84 +2979,89 @@
         <v>46120</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>エンボス+エンボス　湖南</t>
-        </is>
+      <c r="O22" t="n">
+        <v>0</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
+          <t>スリット+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q22" s="3" t="n"/>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>（10）</t>
-        </is>
-      </c>
-      <c r="S22" s="3" t="n"/>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="n"/>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" t="inlineStr">
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>（10.12）</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="n"/>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="n"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="n"/>
+      <c r="Y22" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="n"/>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>（2026/4/1）</t>
-        </is>
-      </c>
-      <c r="AA22" s="3" t="n"/>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC22" s="3" t="n"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE22" s="3" t="n"/>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG22" s="3" t="n"/>
+      <c r="Z22" s="3" t="n"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>（2026/4/2）</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="n"/>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="n"/>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="n"/>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JR260401</t>
+          <t>JR260402</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2979,7 +3085,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95  LG</t>
+          <t>40040-R10W- 870X 95</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -2993,74 +3099,79 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>スリット+スリット機1　湖南</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q23" s="3" t="n"/>
-      <c r="R23" t="inlineStr">
+      <c r="R23" s="3" t="n"/>
+      <c r="S23" t="inlineStr">
         <is>
           <t>（10.12）</t>
         </is>
       </c>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" t="inlineStr">
+      <c r="T23" s="3" t="n"/>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="n"/>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="n"/>
+      <c r="Y23" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" t="inlineStr">
+      <c r="Z23" s="3" t="n"/>
+      <c r="AA23" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA23" s="3" t="n"/>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC23" s="3" t="n"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE23" s="3" t="n"/>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG23" s="3" t="n"/>
+      <c r="AB23" s="3" t="n"/>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="n"/>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="n"/>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -3070,12 +3181,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JR260401</t>
+          <t>Y4-3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>分割</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3084,17 +3195,17 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="F24" t="n">
-        <v>950</v>
+        <v>2800</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95  LG</t>
+          <t>19022-FG00- 940X200F-AGR2M</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -3104,81 +3215,90 @@
         <v>46120</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
       <c r="N24" t="n">
         <v>0</v>
       </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>梱包+スリット機1　湖南</t>
-        </is>
+      <c r="O24" t="n">
+        <v>0</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>（2）</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="n"/>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>（0）</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" t="inlineStr">
+          <t>分割+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>（15）</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="n"/>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="n"/>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="n"/>
+      <c r="Y24" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="n"/>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>（2026/4/2）</t>
-        </is>
-      </c>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC24" s="3" t="n"/>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE24" s="3" t="n"/>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG24" s="3" t="n"/>
+      <c r="Z24" s="3" t="n"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>（2026/4/1）</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="n"/>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="n"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="n"/>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n"/>
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>JR260401</t>
@@ -3186,12 +3306,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>スリット機1　湖南</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3201,7 +3321,7 @@
         <v>950</v>
       </c>
       <c r="G25" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -3219,77 +3339,86 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>SEC+SEC機　湖南</t>
-        </is>
+      <c r="O25" t="n">
+        <v>0</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q25" s="3" t="n"/>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>（25）</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" t="inlineStr">
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>（0）</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="n"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="n"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="n"/>
+      <c r="Y25" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" t="inlineStr">
+      <c r="Z25" s="3" t="n"/>
+      <c r="AA25" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC25" s="3" t="n"/>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE25" s="3" t="n"/>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG25" s="3" t="n"/>
+      <c r="AB25" s="3" t="n"/>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="n"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="n"/>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n"/>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>JR260402</t>
@@ -3297,7 +3426,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>スリット</t>
+          <t>梱包</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3306,13 +3435,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="F26" t="n">
         <v>950</v>
       </c>
       <c r="G26" t="n">
-        <v>10.12</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3330,94 +3459,95 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
       <c r="N26" t="n">
         <v>0</v>
       </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>スリット+スリット機1　湖南</t>
-        </is>
+      <c r="O26" t="n">
+        <v>0</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
+          <t>梱包+スリット機1　湖南</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q26" s="3" t="n"/>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>（10.12）</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" t="inlineStr">
+      <c r="R26" s="3" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>（0）</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="n"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="n"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="n"/>
+      <c r="Y26" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" t="inlineStr">
+      <c r="Z26" s="3" t="n"/>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC26" s="3" t="n"/>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE26" s="3" t="n"/>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG26" s="3" t="n"/>
+      <c r="AB26" s="3" t="n"/>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="n"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="n"/>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="A27" s="3" t="n"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JR260402</t>
+          <t>JR260401</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>梱包</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>スリット機1　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3427,11 +3557,11 @@
         <v>950</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>40040-R10W- 870X 95</t>
+          <t>40040-R10W- 870X 95  LG</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -3445,74 +3575,79 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>梱包+スリット機1　湖南</t>
-        </is>
+      <c r="O27" t="n">
+        <v>0</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q27" s="3" t="n"/>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>（0）</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" t="inlineStr">
+      <c r="R27" s="3" t="n"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>（25）</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="n"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="n"/>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="n"/>
+      <c r="Y27" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" t="inlineStr">
+      <c r="Z27" s="3" t="n"/>
+      <c r="AA27" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC27" s="3" t="n"/>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE27" s="3" t="n"/>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG27" s="3" t="n"/>
+      <c r="AB27" s="3" t="n"/>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="n"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="n"/>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -3556,104 +3691,109 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
+          <t>SEC,梱包,スリット</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
       <c r="N28" t="n">
         <v>0</v>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>SEC+SEC機　湖南</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q28" s="3" t="n"/>
-      <c r="R28" t="inlineStr">
+      <c r="R28" s="3" t="n"/>
+      <c r="S28" t="inlineStr">
         <is>
           <t>（25）</t>
         </is>
       </c>
-      <c r="S28" s="3" t="n"/>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" t="inlineStr">
+      <c r="T28" s="3" t="n"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="n"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="n"/>
+      <c r="Y28" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" t="inlineStr">
+      <c r="Z28" s="3" t="n"/>
+      <c r="AA28" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA28" s="3" t="n"/>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC28" s="3" t="n"/>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE28" s="3" t="n"/>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG28" s="3" t="n"/>
+      <c r="AB28" s="3" t="n"/>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="n"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="n"/>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>T4-1</t>
+          <t>Y4-3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>エンボス</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EC機　湖南</t>
+          <t>エンボス　湖南</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="F29" t="n">
-        <v>1000</v>
+        <v>2800</v>
       </c>
       <c r="G29" t="n">
-        <v>18.06</v>
+        <v>10</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>30040-JG00-1030X200F-ABK0Q</t>
+          <t>19022-FG00- 940X200F-AGR2M</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -3663,78 +3803,83 @@
         <v>46120</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
+          <t>分割,エンボス</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
       <c r="N29" t="n">
         <v>0</v>
       </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>EC+EC機　湖南</t>
-        </is>
+      <c r="O29" t="n">
+        <v>0</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>（3）</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="n"/>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>（18.06）</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" t="inlineStr">
+          <t>エンボス+エンボス　湖南</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>（2）</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="n"/>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="n"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="n"/>
+      <c r="Y29" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>（2026/4/3）</t>
-        </is>
-      </c>
-      <c r="AA29" s="3" t="n"/>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC29" s="3" t="n"/>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE29" s="3" t="n"/>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG29" s="3" t="n"/>
+      <c r="Z29" s="3" t="n"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>（2026/4/1）</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="n"/>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="n"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="n"/>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n"/>
@@ -3778,104 +3923,109 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>EC+EC機　湖南</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q30" s="3" t="n"/>
-      <c r="R30" t="inlineStr">
+      <c r="R30" s="3" t="n"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>（18.06）</t>
         </is>
       </c>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" t="inlineStr">
+      <c r="T30" s="3" t="n"/>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="n"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="n"/>
+      <c r="Y30" t="inlineStr">
         <is>
           <t>（2026/4/10）</t>
         </is>
       </c>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" t="inlineStr">
+      <c r="Z30" s="3" t="n"/>
+      <c r="AA30" t="inlineStr">
         <is>
           <t>（2026/4/2）</t>
         </is>
       </c>
-      <c r="AA30" s="3" t="n"/>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC30" s="3" t="n"/>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE30" s="3" t="n"/>
-      <c r="AF30" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG30" s="3" t="n"/>
+      <c r="AB30" s="3" t="n"/>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="n"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="n"/>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>W4-2</t>
+          <t>Y4-8</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>検査</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>9300</v>
+        <v>14000</v>
       </c>
       <c r="F31" t="n">
-        <v>9300</v>
+        <v>28000</v>
       </c>
       <c r="G31" t="n">
-        <v>9.039999999999999</v>
+        <v>25</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>15020-JX5R-1440X300F-A   R</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="I31" s="2" t="n">
@@ -3885,108 +4035,113 @@
         <v>46122</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
+          <t>SEC</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
       <c r="N31" t="n">
         <v>0</v>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>検査+熱融着機　湖南</t>
-        </is>
+      <c r="O31" t="n">
+        <v>0</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q31" s="3" t="n"/>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>（9.04）</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="n"/>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" t="inlineStr">
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>（3）</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>（25）</t>
+        </is>
+      </c>
+      <c r="T31" s="3" t="n"/>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="n"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="n"/>
+      <c r="Y31" t="inlineStr">
         <is>
           <t>（2026/4/10）</t>
         </is>
       </c>
-      <c r="Y31" s="3" t="n"/>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>（2026/4/2）</t>
-        </is>
-      </c>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC31" s="3" t="n"/>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE31" s="3" t="n"/>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG31" s="3" t="n"/>
+      <c r="Z31" s="3" t="n"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>（2026/4/7）</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="n"/>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="n"/>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="n"/>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Y4-8</t>
+          <t>W4-2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>検査</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>14000</v>
+        <v>9300</v>
       </c>
       <c r="F32" t="n">
-        <v>28000</v>
+        <v>9300</v>
       </c>
       <c r="G32" t="n">
-        <v>25</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>15020-JX5R-1440X300F-A   R</t>
         </is>
       </c>
       <c r="I32" s="2" t="n">
@@ -3996,78 +4151,83 @@
         <v>46122</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>46119</v>
+        <v>46114</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
       <c r="N32" t="n">
         <v>0</v>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>SEC+SEC機　湖南</t>
-        </is>
+      <c r="O32" t="n">
+        <v>0</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>（3）</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="n"/>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>（25）</t>
-        </is>
-      </c>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" t="inlineStr">
+          <t>検査+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="n"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>（9.04）</t>
+        </is>
+      </c>
+      <c r="T32" s="3" t="n"/>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="n"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n"/>
+      <c r="Y32" t="inlineStr">
         <is>
           <t>（2026/4/10）</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>（2026/4/7）</t>
-        </is>
-      </c>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC32" s="3" t="n"/>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE32" s="3" t="n"/>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG32" s="3" t="n"/>
+      <c r="Z32" s="3" t="n"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>（2026/4/2）</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="n"/>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="n"/>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="n"/>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n"/>
@@ -4111,74 +4271,79 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
       <c r="N33" t="n">
         <v>0</v>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q33" s="3" t="n"/>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="3" t="n"/>
+      <c r="S33" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" t="inlineStr">
+      <c r="T33" s="3" t="n"/>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="n"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="n"/>
+      <c r="Y33" t="inlineStr">
         <is>
           <t>（2026/4/14）</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="n"/>
-      <c r="Z33" t="inlineStr">
+      <c r="Z33" s="3" t="n"/>
+      <c r="AA33" t="inlineStr">
         <is>
           <t>（2026/4/6）</t>
         </is>
       </c>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC33" s="3" t="n"/>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE33" s="3" t="n"/>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG33" s="3" t="n"/>
+      <c r="AB33" s="3" t="n"/>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="n"/>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="n"/>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n"/>
@@ -4222,74 +4387,79 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
       <c r="N34" t="n">
         <v>0</v>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q34" s="3" t="n"/>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="3" t="n"/>
+      <c r="S34" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S34" s="3" t="n"/>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" t="inlineStr">
+      <c r="T34" s="3" t="n"/>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="n"/>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="n"/>
+      <c r="Y34" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" s="3" t="n"/>
+      <c r="AA34" t="inlineStr">
         <is>
           <t>（2026/4/7）</t>
         </is>
       </c>
-      <c r="AA34" s="3" t="n"/>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC34" s="3" t="n"/>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE34" s="3" t="n"/>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG34" s="3" t="n"/>
+      <c r="AB34" s="3" t="n"/>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="n"/>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="n"/>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n"/>
@@ -4333,74 +4503,79 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M35" t="n">
-        <v>0</v>
-      </c>
       <c r="N35" t="n">
         <v>0</v>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="3" t="n"/>
+      <c r="S35" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S35" s="3" t="n"/>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" t="inlineStr">
+      <c r="T35" s="3" t="n"/>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="n"/>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="n"/>
+      <c r="Y35" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" s="3" t="n"/>
+      <c r="AA35" t="inlineStr">
         <is>
           <t>（2026/4/9）</t>
         </is>
       </c>
-      <c r="AA35" s="3" t="n"/>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC35" s="3" t="n"/>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE35" s="3" t="n"/>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG35" s="3" t="n"/>
+      <c r="AB35" s="3" t="n"/>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="n"/>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="n"/>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -4444,74 +4619,79 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
+          <t>スライス</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" t="n">
         <v>0</v>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>スライス+スライス機1　湖南</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>（2）</t>
         </is>
       </c>
-      <c r="Q36" s="3" t="n"/>
-      <c r="R36" t="inlineStr">
+      <c r="R36" s="3" t="n"/>
+      <c r="S36" t="inlineStr">
         <is>
           <t>（16.12）</t>
         </is>
       </c>
-      <c r="S36" s="3" t="n"/>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="n"/>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" t="inlineStr">
+      <c r="T36" s="3" t="n"/>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="n"/>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="n"/>
+      <c r="Y36" t="inlineStr">
         <is>
           <t>（2026/4/20）</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="n"/>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" s="3" t="n"/>
+      <c r="AA36" t="inlineStr">
         <is>
           <t>（2026/4/8）</t>
         </is>
       </c>
-      <c r="AA36" s="3" t="n"/>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC36" s="3" t="n"/>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE36" s="3" t="n"/>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG36" s="3" t="n"/>
+      <c r="AB36" s="3" t="n"/>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="n"/>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="n"/>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n"/>
@@ -4555,74 +4735,79 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
       <c r="N37" t="n">
         <v>0</v>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>EC+EC機　湖南</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q37" s="3" t="n"/>
-      <c r="R37" t="inlineStr">
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" t="inlineStr">
         <is>
           <t>（18.06）</t>
         </is>
       </c>
-      <c r="S37" s="3" t="n"/>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U37" s="3" t="n"/>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" t="inlineStr">
+      <c r="T37" s="3" t="n"/>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="n"/>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="n"/>
+      <c r="Y37" t="inlineStr">
         <is>
           <t>（2026/4/20）</t>
         </is>
       </c>
-      <c r="Y37" s="3" t="n"/>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" s="3" t="n"/>
+      <c r="AA37" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="AA37" s="3" t="n"/>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC37" s="3" t="n"/>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE37" s="3" t="n"/>
-      <c r="AF37" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG37" s="3" t="n"/>
+      <c r="AB37" s="3" t="n"/>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="n"/>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="n"/>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n"/>
@@ -4666,80 +4851,85 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
       <c r="N38" t="n">
         <v>0</v>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>検査+熱融着機　湖南</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>（1）</t>
         </is>
       </c>
-      <c r="Q38" s="3" t="n"/>
-      <c r="R38" t="inlineStr">
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" t="inlineStr">
         <is>
           <t>（9.04）</t>
         </is>
       </c>
-      <c r="S38" s="3" t="n"/>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="n"/>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" t="inlineStr">
+      <c r="T38" s="3" t="n"/>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="n"/>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="n"/>
+      <c r="Y38" t="inlineStr">
         <is>
           <t>（2026/4/20）</t>
         </is>
       </c>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" s="3" t="n"/>
+      <c r="AA38" t="inlineStr">
         <is>
           <t>（2026/4/3）</t>
         </is>
       </c>
-      <c r="AA38" s="3" t="n"/>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC38" s="3" t="n"/>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE38" s="3" t="n"/>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG38" s="3" t="n"/>
+      <c r="AB38" s="3" t="n"/>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="n"/>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="n"/>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Y4-9</t>
+          <t>Y4-10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4753,17 +4943,17 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="F39" t="n">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="G39" t="n">
         <v>25</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 870X200F-ABG1C</t>
+          <t>0R040-8Y0B- 680X200F-AGA1C</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -4777,74 +4967,79 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
+          <t>接続,SEC</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
       <c r="N39" t="n">
         <v>0</v>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>SEC+SEC機　湖南</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q39" s="3" t="n"/>
-      <c r="R39" t="inlineStr">
+      <c r="R39" s="3" t="n"/>
+      <c r="S39" t="inlineStr">
         <is>
           <t>（25）</t>
         </is>
       </c>
-      <c r="S39" s="3" t="n"/>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="n"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" t="inlineStr">
+      <c r="T39" s="3" t="n"/>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="n"/>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="n"/>
+      <c r="Y39" t="inlineStr">
         <is>
           <t>（2026/4/21）</t>
         </is>
       </c>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" s="3" t="n"/>
+      <c r="AA39" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="AA39" s="3" t="n"/>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC39" s="3" t="n"/>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE39" s="3" t="n"/>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG39" s="3" t="n"/>
+      <c r="AB39" s="3" t="n"/>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="n"/>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="n"/>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n"/>
@@ -4855,12 +5050,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>熱融着</t>
+          <t>SEC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>熱融着機　湖南</t>
+          <t>SEC機　湖南</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4870,7 +5065,7 @@
         <v>2000</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4888,74 +5083,79 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
+          <t>熱融着,SEC</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>熱融着+熱融着機　湖南</t>
-        </is>
+      <c r="O40" t="n">
+        <v>0</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>（1）</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="n"/>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>（10）</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" t="inlineStr">
+          <t>SEC+SEC機　湖南</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>（3）</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="n"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>（25）</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="n"/>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n"/>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="n"/>
+      <c r="Y40" t="inlineStr">
         <is>
           <t>（2026/4/21）</t>
         </is>
       </c>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" s="3" t="n"/>
+      <c r="AA40" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="AA40" s="3" t="n"/>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC40" s="3" t="n"/>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE40" s="3" t="n"/>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG40" s="3" t="n"/>
+      <c r="AB40" s="3" t="n"/>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="n"/>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="n"/>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n"/>
@@ -4966,12 +5166,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SEC</t>
+          <t>接続</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>SEC機　湖南</t>
+          <t>熱融着機　湖南</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4981,7 +5181,7 @@
         <v>1600</v>
       </c>
       <c r="G41" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4999,85 +5199,90 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
+          <t>接続,SEC</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
       <c r="N41" t="n">
         <v>0</v>
       </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>SEC+SEC機　湖南</t>
-        </is>
+      <c r="O41" t="n">
+        <v>0</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>（3）</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="n"/>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>（25）</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="n"/>
-      <c r="V41" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="n"/>
-      <c r="X41" t="inlineStr">
+          <t>接続+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>（1）</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="n"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>（15）</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="n"/>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="n"/>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="n"/>
+      <c r="Y41" t="inlineStr">
         <is>
           <t>（2026/4/21）</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="3" t="n"/>
+      <c r="AA41" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="AA41" s="3" t="n"/>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC41" s="3" t="n"/>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE41" s="3" t="n"/>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG41" s="3" t="n"/>
+      <c r="AB41" s="3" t="n"/>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="n"/>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="n"/>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Y4-10</t>
+          <t>Y4-9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>接続</t>
+          <t>熱融着</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5086,17 +5291,17 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="F42" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
       <c r="G42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0R040-8Y0B- 680X200F-AGA1C</t>
+          <t>0R040-8Y0B- 870X200F-ABG1C</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -5110,74 +5315,79 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
+          <t>熱融着,SEC</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
         <v>0</v>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>接続+熱融着機　湖南</t>
-        </is>
+      <c r="O42" t="n">
+        <v>0</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
+          <t>熱融着+熱融着機　湖南</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
           <t>（1）</t>
         </is>
       </c>
-      <c r="Q42" s="3" t="n"/>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>（15）</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" t="inlineStr">
+      <c r="R42" s="3" t="n"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>（10）</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="n"/>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="n"/>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="n"/>
+      <c r="Y42" t="inlineStr">
         <is>
           <t>（2026/4/21）</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="3" t="n"/>
+      <c r="AA42" t="inlineStr">
         <is>
           <t>（2026/4/15）</t>
         </is>
       </c>
-      <c r="AA42" s="3" t="n"/>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC42" s="3" t="n"/>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE42" s="3" t="n"/>
-      <c r="AF42" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG42" s="3" t="n"/>
+      <c r="AB42" s="3" t="n"/>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="n"/>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="n"/>
+      <c r="AG42" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n"/>
@@ -5221,74 +5431,79 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
       <c r="N43" t="n">
         <v>0</v>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>EC+EC機　湖南</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q43" s="3" t="n"/>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" t="inlineStr">
         <is>
           <t>（18.06）</t>
         </is>
       </c>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" t="inlineStr">
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="n"/>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="n"/>
+      <c r="Y43" t="inlineStr">
         <is>
           <t>（2026/4/23）</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="n"/>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" s="3" t="n"/>
+      <c r="AA43" t="inlineStr">
         <is>
           <t>（2026/4/13）</t>
         </is>
       </c>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC43" s="3" t="n"/>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE43" s="3" t="n"/>
-      <c r="AF43" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG43" s="3" t="n"/>
+      <c r="AB43" s="3" t="n"/>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="n"/>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="n"/>
+      <c r="AG43" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n"/>
@@ -5332,74 +5547,79 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
+          <t>EC,検査</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
           <t>0:未完</t>
         </is>
       </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
       <c r="N44" t="n">
         <v>0</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="inlineStr">
         <is>
           <t>EC+EC機　湖南</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>（3）</t>
         </is>
       </c>
-      <c r="Q44" s="3" t="n"/>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" t="inlineStr">
         <is>
           <t>（18.06）</t>
         </is>
       </c>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" t="inlineStr">
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="n"/>
+      <c r="Y44" t="inlineStr">
         <is>
           <t>（2026/4/27）</t>
         </is>
       </c>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" t="inlineStr">
+      <c r="Z44" s="3" t="n"/>
+      <c r="AA44" t="inlineStr">
         <is>
           <t>（2026/4/13）</t>
         </is>
       </c>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AC44" s="3" t="n"/>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AE44" s="3" t="n"/>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>（―）</t>
-        </is>
-      </c>
-      <c r="AG44" s="3" t="n"/>
+      <c r="AB44" s="3" t="n"/>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="n"/>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="n"/>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>（―）</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
